--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalcmultiday.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalcmultiday.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,19 +146,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -801,11 +792,11 @@
       <c r="F4" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="12" t="n">
-        <v>81.7</v>
+      <c r="G4" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -813,37 +804,37 @@
       <c r="J4" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>8</v>
+      <c r="K4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q4" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="S4" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="T4" s="3" t="n">
+      <c r="R4" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="S4" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="T4" s="9" t="n">
         <v>42.5</v>
       </c>
-      <c r="U4" s="12" t="n">
+      <c r="U4" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="9" t="n">
@@ -852,7 +843,7 @@
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="12" t="n">
+      <c r="X4" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -890,7 +881,7 @@
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -898,53 +889,53 @@
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>1.2</v>
       </c>
       <c r="L5" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="17" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+      <c r="M5" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q5" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>2</v>
+      <c r="S5" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>1.4</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X5" s="9" t="n">
+      <c r="W5" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="X5" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="Y5" s="3" t="n">
         <v>80.5</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>4.4</v>
+      <c r="Z5" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -966,12 +957,12 @@
         <v>25.9</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="G6" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G6" s="9" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -981,10 +972,10 @@
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>16.5</v>
+        <v>1.1</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>11.1</v>
@@ -993,43 +984,43 @@
         <v>11</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>98.5</v>
+        <v>99.3</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q6" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>11.9</v>
+      <c r="S6" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="T6" s="9" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y6" s="3" t="n">
+      <c r="W6" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="X6" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y6" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="Z6" s="3" t="n">
-        <v>2.9</v>
+      <c r="Z6" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1066,40 +1057,40 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>21.1</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="N7" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+      <c r="M7" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="3" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>4.8</v>
+      <c r="S7" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v>3.3</v>
       </c>
       <c r="V7" s="9" t="n">
         <v>18.9</v>
@@ -1107,14 +1098,14 @@
       <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="12" t="n">
+      <c r="X7" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1136,16 +1127,16 @@
         <v>26.3</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.7</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1153,46 +1144,46 @@
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q8" s="12" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R8" s="3" t="n">
+      <c r="N8" s="9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R8" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>6</v>
+      <c r="S8" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="17" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="X8" s="12" t="n">
+      <c r="W8" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1215,7 +1206,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>174.7</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>128.9</v>
@@ -1226,11 +1217,11 @@
       <c r="F9" s="9" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>13.9</v>
+      <c r="G9" s="9" t="n">
+        <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>140.6</v>
+        <v>40.6</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.9</v>
@@ -1238,14 +1229,14 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.7</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="M9" s="18" t="n">
-        <v>551.2</v>
+        <v>57.2</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>766.1</v>
@@ -1254,14 +1245,14 @@
         <v>484.9</v>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="18" t="n">
+      <c r="Q9" s="9" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="18" t="n">
-        <v>185.3</v>
+      <c r="R9" s="9" t="n">
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1272,14 +1263,14 @@
       <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="18" t="n">
+      <c r="W9" s="15" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>414.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1298,7 +1289,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8349.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>25.8</v>
@@ -1318,44 +1309,44 @@
       <c r="I10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="12" t="n">
-        <v>9.4</v>
+      <c r="J10" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="M10" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q10" s="18" t="n">
+      <c r="N10" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q10" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="18" t="n">
-        <v>117.7</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>6.7</v>
+      <c r="R10" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S10" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="18" t="n">
+      <c r="W10" s="15" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1379,7 +1370,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.3</v>
+        <v>509.5</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>27.3</v>
@@ -1390,26 +1381,26 @@
       <c r="F11" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>18.6</v>
+      <c r="G11" s="9" t="n">
+        <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1420,35 +1411,35 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="12" t="n">
+      <c r="Q11" s="9" t="n">
         <v>26.3</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S11" s="12" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S11" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="T11" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U11" s="12" t="n">
+      <c r="T11" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>9</v>
+      <c r="X11" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="Z11" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1464,7 +1455,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>508.7</v>
+        <v>506.7</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>25.9</v>
@@ -1482,18 +1473,18 @@
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M12" s="12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1505,35 +1496,35 @@
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>25.4</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="S12" s="12" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>20.4</v>
+      <c r="S12" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v>14.8</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Y12" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v>12.2</v>
+      <c r="W12" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X12" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y12" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z12" s="9" t="n">
+        <v>8.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1552,25 +1543,25 @@
         <v>357.9</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>99.40000000000001</v>
+        <v>7.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0.5</v>
@@ -1579,9 +1570,9 @@
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N13" s="12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N13" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
@@ -1590,20 +1581,20 @@
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>185.4</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>13</v>
+      <c r="S13" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="V13" s="9" t="n">
         <v>19.6</v>
@@ -1637,13 +1628,13 @@
         <v>227</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>10.5</v>
@@ -1651,19 +1642,19 @@
       <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>28.5</v>
+      <c r="I14" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="L14" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M14" s="12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1673,37 +1664,37 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q14" s="17" t="n">
-        <v>84.90000000000001</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>14.9</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>14.7</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>0.6</v>
+        <v>16.7</v>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="V14" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X14" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y14" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>1</v>
+      <c r="W14" s="9" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X14" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="Y14" s="9" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="Z14" s="9" t="n">
+        <v>-0.8</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1719,19 +1710,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>631</v>
+        <v>31</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>50.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1740,19 +1731,19 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="17" t="n">
-        <v>77.40000000000001</v>
+      <c r="L15" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1760,20 +1751,20 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S15" s="12" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="S15" s="9" t="n">
         <v>15.7</v>
       </c>
-      <c r="T15" s="3" t="n">
+      <c r="T15" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="12" t="n">
-        <v>17.8</v>
+      <c r="U15" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>20.7</v>
@@ -1808,12 +1799,12 @@
         <v>128</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>56.3</v>
+        <v>56.8</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="G16" s="3" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="G16" s="9" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1825,26 +1816,26 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="18" t="n">
+      <c r="K16" s="15" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M16" s="18" t="n">
+      <c r="L16" s="15" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="M16" s="15" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>489.8</v>
+        <v>89</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="18" t="n">
-        <v>1111</v>
+      <c r="Q16" s="9" t="n">
+        <v>111</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>82.2</v>
@@ -1853,16 +1844,16 @@
         <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>603.9</v>
+        <v>60.9</v>
       </c>
       <c r="V16" s="9" t="n">
         <v>98.2</v>
       </c>
-      <c r="W16" s="18" t="n">
-        <v>801.9</v>
+      <c r="W16" s="9" t="n">
+        <v>78.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
@@ -1905,56 +1896,56 @@
         <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>29.4</v>
+        <v>2.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="18" t="n">
+      <c r="L17" s="15" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="18" t="n">
+      <c r="M17" s="15" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Q17" s="18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q17" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>362</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>18.2</v>
+      <c r="S17" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="18" t="n">
+      <c r="W17" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>872.8</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+      <c r="X17" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Y17" s="9" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="Z17" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1961,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>845.5</v>
+        <v>45.5</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>25.9</v>
@@ -1979,21 +1970,21 @@
         <v>10.9</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>13</v>
+        <v>18.7</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="L18" s="9" t="n">
@@ -2014,32 +2005,32 @@
       <c r="Q18" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S18" s="12" t="n">
+      <c r="R18" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="S18" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="T18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U18" s="12" t="n">
+      <c r="T18" s="9" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U18" s="9" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="12" t="n">
+      <c r="W18" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="12" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y18" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+      <c r="X18" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y18" s="9" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Z18" s="9" t="n">
+        <v>7.3</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2066,8 +2057,8 @@
       <c r="F19" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>17.9</v>
+      <c r="G19" s="9" t="n">
+        <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2078,10 +2069,10 @@
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>11.2</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2099,17 +2090,17 @@
       <c r="Q19" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S19" s="3" t="n">
+      <c r="R19" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="S19" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="T19" s="3" t="n">
+      <c r="T19" s="9" t="n">
         <v>48.5</v>
       </c>
-      <c r="U19" s="12" t="n">
-        <v>7.2</v>
+      <c r="U19" s="9" t="n">
+        <v>17.2</v>
       </c>
       <c r="V19" s="9" t="n">
         <v>21.2</v>
@@ -2157,59 +2148,59 @@
       <c r="H20" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>33.3</v>
+      <c r="I20" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="17" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N20" s="12" t="n">
+      <c r="M20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S20" s="3" t="n">
+      <c r="R20" s="9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="S20" s="9" t="n">
         <v>15.3</v>
       </c>
-      <c r="T20" s="3" t="n">
+      <c r="T20" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="12" t="n">
-        <v>222.4</v>
+      <c r="U20" s="9" t="n">
+        <v>22.4</v>
       </c>
       <c r="V20" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X20" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y20" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v>7.6</v>
+      <c r="W20" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X20" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Y20" s="9" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="Z20" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2230,13 +2221,13 @@
       <c r="D21" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="E21" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G21" s="9" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2248,52 +2239,52 @@
       <c r="J21" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P21" s="3" t="n">
+      <c r="O21" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P21" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q21" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S21" s="3" t="n">
+      <c r="R21" s="9" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S21" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="T21" s="3" t="n">
+      <c r="T21" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>1.6</v>
+      <c r="U21" s="9" t="n">
+        <v>16.2</v>
       </c>
       <c r="V21" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="W21" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="X21" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Y21" s="3" t="n">
+      <c r="W21" s="9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X21" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y21" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="Z21" s="3" t="n">
+      <c r="Z21" s="9" t="n">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2310,22 +2301,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>989</v>
+        <v>9</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="17" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="E22" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G22" s="9" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>83.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
@@ -2333,53 +2324,53 @@
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" s="12" t="n">
+      <c r="K22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P22" s="3" t="n">
+      <c r="N22" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="P22" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="S22" s="3" t="n">
+      <c r="R22" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S22" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="T22" s="3" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="U22" s="3" t="n">
+      <c r="T22" s="9" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="U22" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="V22" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="9" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="12" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>139.7</v>
+      <c r="X22" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y22" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z22" s="9" t="n">
+        <v>9.5</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2395,55 +2386,55 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2322.3</v>
+        <v>2320.3</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="18" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="F23" s="18" t="n">
+      <c r="E23" s="9" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F23" s="9" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+      <c r="G23" s="9" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="K23" s="18" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K23" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M23" s="18" t="n">
-        <v>161.8</v>
+      <c r="L23" s="9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="M23" s="15" t="n">
+        <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
+        <v>93</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="18" t="n">
-        <v>85</v>
+      <c r="R23" s="9" t="n">
+        <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>7.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2454,7 +2445,7 @@
       <c r="V23" s="9" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="18" t="n">
+      <c r="W23" s="9" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2501,19 +2492,19 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L24" s="18" t="n">
+      <c r="L24" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="18" t="n">
+      <c r="M24" s="15" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2524,32 +2515,32 @@
       <c r="Q24" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="18" t="n">
+      <c r="R24" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>17.8</v>
+      <c r="S24" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>13.1</v>
       </c>
       <c r="V24" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="18" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>8.199999999999999</v>
+      <c r="W24" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X24" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y24" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z24" s="9" t="n">
+        <v>5.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2576,8 +2567,8 @@
       <c r="F25" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>10.9</v>
+      <c r="G25" s="9" t="n">
+        <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
@@ -2588,23 +2579,23 @@
       <c r="J25" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>6.4</v>
+      <c r="K25" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>24.7</v>
@@ -2650,7 +2641,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>349.1</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>24.4</v>
@@ -2667,29 +2658,29 @@
       <c r="H26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>23.4</v>
+      <c r="I26" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0.9</v>
+      <c r="N26" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>21</v>
@@ -2709,17 +2700,17 @@
       <c r="V26" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X26" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y26" s="9" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="Z26" s="9" t="n">
-        <v>8.199999999999999</v>
+      <c r="W26" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2738,16 +2729,16 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>24</v>
+      <c r="G27" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>8.4</v>
@@ -2756,25 +2747,25 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>7.1</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="N27" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>0.4</v>
+      <c r="N27" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P27" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>17.6</v>
@@ -2794,17 +2785,17 @@
       <c r="V27" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="X27" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y27" s="9" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="Z27" s="9" t="n">
-        <v>0.9</v>
+      <c r="X27" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2831,11 +2822,11 @@
       <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>15.9</v>
+      <c r="G28" s="9" t="n">
+        <v>15.5</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>2.4</v>
@@ -2843,11 +2834,11 @@
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="9" t="n">
         <v>5.5</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="M28" s="9" t="n">
         <v>13.3</v>
@@ -2856,10 +2847,10 @@
         <v>15.3</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>98.7</v>
+        <v>99.3</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>22.9</v>
@@ -2879,17 +2870,17 @@
       <c r="V28" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y28" s="9" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="Z28" s="9" t="n">
-        <v>1</v>
+      <c r="X28" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2905,7 +2896,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>593.3</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>28.8</v>
@@ -2916,8 +2907,8 @@
       <c r="F29" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>1.8</v>
+      <c r="G29" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2928,23 +2919,23 @@
       <c r="J29" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="N29" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>2.6</v>
+      <c r="N29" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>27</v>
@@ -2965,16 +2956,16 @@
         <v>22.8</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>17.3</v>
+        <v>14.7</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>19.7</v>
+        <v>16.7</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>71.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>8</v>
+        <v>11.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2993,15 +2984,15 @@
         <v>228.4</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>131.8</v>
+        <v>131.2</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>51.4</v>
+        <v>52.1</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="9" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
@@ -3013,14 +3004,14 @@
       <c r="J30" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="K30" s="18" t="n">
+      <c r="K30" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="M30" s="18" t="n">
-        <v>56.7</v>
+        <v>57.2</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>65.90000000000001</v>
@@ -3041,25 +3032,25 @@
         <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>314.8</v>
+        <v>14.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.4</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="15" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="X30" s="9" t="n">
-        <v>522</v>
-      </c>
-      <c r="Y30" s="9" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="Z30" s="9" t="n">
-        <v>506.8</v>
+      <c r="X30" s="3" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>35</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3075,7 +3066,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>26.2</v>
@@ -3100,49 +3091,49 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="M31" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="O31" s="9" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="P31" s="9" t="n">
+      <c r="N31" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="R31" s="9" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="S31" s="12" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="U31" s="12" t="n">
-        <v>111.4</v>
+        <v>17.3</v>
+      </c>
+      <c r="S31" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>7.7</v>
       </c>
       <c r="V31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="15" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Y31" s="9" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="Z31" s="9" t="n">
-        <v>4.6</v>
+      <c r="X31" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>730.2</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3167,7 +3158,7 @@
         <v>10.2</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>17.7</v>
@@ -3181,11 +3172,11 @@
       <c r="J32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>20.5</v>
+      <c r="K32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>10.5</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>10.2</v>
@@ -3193,39 +3184,39 @@
       <c r="N32" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O32" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>26.46</v>
+      <c r="O32" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="R32" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T32" s="9" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="V32" s="3" t="n">
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="n">
-        <v>171.8</v>
+      <c r="X32" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="Y32" s="9" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="Z32" s="9" t="n">
+        <v>5.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3256,61 +3247,61 @@
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>14.9</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q33" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N33" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P33" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="S33" s="9" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>19.9</v>
+      <c r="S33" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" s="9" t="n">
+        <v>19.4</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="X33" s="12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Y33" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z33" s="3" t="n">
-        <v>14</v>
+      <c r="X33" s="9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Y33" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z33" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3326,7 +3317,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.9</v>
+        <v>329.1</v>
       </c>
       <c r="D34" s="9" t="n">
         <v>23.3</v>
@@ -3340,62 +3331,62 @@
       <c r="G34" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="H34" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K34" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K34" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>16</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O34" s="3" t="n">
+      <c r="N34" s="9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O34" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P34" s="3" t="n">
+      <c r="P34" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="R34" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="S34" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T34" s="9" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="U34" s="9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V34" s="12" t="n">
-        <v>28.7</v>
+      <c r="S34" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V34" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y34" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>3.8</v>
+      <c r="X34" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y34" s="9" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="Z34" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3434,7 +3425,7 @@
       <c r="J35" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
@@ -3444,43 +3435,43 @@
         <v>12.9</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q35" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="9" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T35" s="9" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="U35" s="9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="V35" s="12" t="n">
+      <c r="S35" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V35" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>16.7</v>
       </c>
-      <c r="X35" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>8</v>
+      <c r="X35" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="Z35" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3502,70 +3493,70 @@
         <v>26.3</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G36" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G36" s="9" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>8.6</v>
+      <c r="K36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>10.6</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="P36" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T36" s="9" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="U36" s="9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V36" s="3" t="n">
+      <c r="S36" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="V36" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="X36" s="12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>11</v>
+      <c r="X36" s="9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y36" s="9" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="Z36" s="9" t="n">
+        <v>7.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3581,7 +3572,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
+        <v>224.4</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>128.5</v>
@@ -3592,36 +3583,36 @@
       <c r="F37" s="9" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>62.6</v>
+      <c r="G37" s="9" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L37" s="18" t="n">
-        <v>63</v>
+      <c r="K37" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>65</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>63.7</v>
+        <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>492</v>
+        <v>92</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="9" t="n">
-        <v>115.9</v>
+      <c r="Q37" s="15" t="n">
+        <v>115.5</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>88.8</v>
@@ -3630,12 +3621,12 @@
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>16.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="18" t="n">
+      <c r="V37" s="9" t="n">
         <v>100.9</v>
       </c>
       <c r="W37" s="9" t="n">
@@ -3645,7 +3636,7 @@
         <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.3</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>34.6</v>
@@ -3664,7 +3655,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>44.8</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>25.7</v>
@@ -3684,10 +3675,12 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="9" t="n">
         <v>13</v>
       </c>
@@ -3698,40 +3691,40 @@
         <v>14.8</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q38" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="15" t="n">
         <v>23.1</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="S38" s="9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T38" s="9" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="U38" s="9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="V38" s="18" t="n">
+      <c r="S38" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V38" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="12" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>6.9</v>
+      <c r="X38" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y38" s="9" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="Z38" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3762,59 +3755,59 @@
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M39" s="9" t="n">
+      <c r="L39" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="12" t="n">
+      <c r="N39" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q39" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="9" t="n">
         <v>18</v>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V39" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W39" s="17" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="Z39" s="3" t="n">
-        <v>176</v>
+      <c r="V39" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W39" s="9" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X39" s="9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Y39" s="9" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="Z39" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3830,7 +3823,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>335.9</v>
+        <v>355.7</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>27.2</v>
@@ -3853,53 +3846,53 @@
       <c r="J40" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="9" t="n">
         <v>10.6</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>10.3</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>10.2</v>
+      <c r="N40" s="9" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="O40" s="9" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P40" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="R40" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S40" s="12" t="n">
+      <c r="R40" s="9" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S40" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="T40" s="3" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="U40" s="3" t="n">
+      <c r="T40" s="9" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="U40" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W40" s="12" t="n">
+      <c r="V40" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="W40" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y40" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="Z40" s="3" t="n">
-        <v>83</v>
+      <c r="X40" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y40" s="9" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="Z40" s="9" t="n">
+        <v>3.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3918,51 +3911,51 @@
         <v>451.2</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>28.94</v>
+        <v>28.4</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G41" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G41" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>51</v>
+      <c r="H41" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="9" t="n">
-        <v>11.1</v>
+      <c r="N41" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Q41" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R41" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="R41" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="12" t="n">
+      <c r="S41" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
@@ -3971,20 +3964,20 @@
       <c r="U41" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="17" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>15.7</v>
+      <c r="W41" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="X41" s="9" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="Y41" s="9" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Z41" s="9" t="n">
+        <v>5.1</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4005,34 +3998,34 @@
       <c r="D42" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="17" t="n">
-        <v>1.1</v>
+      <c r="E42" s="9" t="n">
+        <v>11.4</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="17" t="n">
-        <v>12.6</v>
+      <c r="G42" s="9" t="n">
+        <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M42" s="9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N42" s="9" t="n">
+      <c r="L42" s="9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M42" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N42" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4041,25 +4034,25 @@
       <c r="P42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q42" s="9" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R42" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S42" s="12" t="n">
+      <c r="Q42" s="14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R42" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S42" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="U42" s="12" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="16" t="inlineStr"/>
+      <c r="W42" s="9" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -4080,25 +4073,25 @@
         <v>0.1</v>
       </c>
       <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="9" t="inlineStr"/>
+      <c r="E43" s="13" t="inlineStr"/>
       <c r="F43" s="9" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="16" t="inlineStr"/>
-      <c r="L43" s="16" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="K43" s="9" t="inlineStr"/>
+      <c r="L43" s="9" t="inlineStr"/>
+      <c r="M43" s="13" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="9" t="inlineStr"/>
-      <c r="R43" s="16" t="inlineStr"/>
+      <c r="Q43" s="13" t="inlineStr"/>
+      <c r="R43" s="9" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="16" t="inlineStr"/>
-      <c r="W43" s="16" t="inlineStr"/>
+      <c r="V43" s="9" t="inlineStr"/>
+      <c r="W43" s="9" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4119,25 +4112,25 @@
         <v>0.1</v>
       </c>
       <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
       <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="16" t="inlineStr"/>
-      <c r="L44" s="16" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="16" t="inlineStr"/>
+      <c r="Q44" s="13" t="inlineStr"/>
+      <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="16" t="inlineStr"/>
-      <c r="W44" s="16" t="inlineStr"/>
+      <c r="V44" s="9" t="inlineStr"/>
+      <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4155,37 +4148,37 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1981.2</v>
+        <v>1911.2</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>41.8</v>
+        <v>109.7</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>41.5</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="G45" s="17" t="n">
-        <v>10.8</v>
+      <c r="G45" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>16.4</v>
+        <v>14.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L45" s="18" t="n">
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="9" t="n">
-        <v>42.5</v>
+      <c r="M45" s="15" t="n">
+        <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>5.1</v>
@@ -4194,12 +4187,12 @@
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Q45" s="9" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="R45" s="18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q45" s="15" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="R45" s="9" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4211,14 +4204,14 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="18" t="n">
-        <v>831.9</v>
-      </c>
-      <c r="W45" s="18" t="n">
-        <v>67.3</v>
+      <c r="V45" s="9" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="W45" s="9" t="n">
+        <v>51</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>62.8</v>
+        <v>66.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4261,33 +4254,33 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L46" s="18" t="n">
-        <v>111.7</v>
-      </c>
-      <c r="M46" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>111100</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="M46" s="15" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="9" t="n">
+      <c r="N46" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q46" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q46" s="15" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="18" t="n">
+      <c r="R46" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="12" t="n">
+      <c r="S46" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
@@ -4296,20 +4289,20 @@
       <c r="U46" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="V46" s="18" t="n">
+      <c r="V46" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="18" t="n">
+      <c r="W46" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>265.7</v>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>81.90000000000001</v>
+      <c r="X46" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y46" s="9" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="Z46" s="9" t="n">
+        <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalcmultiday.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalcmultiday.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -162,9 +162,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -808,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M4" s="9" t="n">
         <v>9.1</v>
@@ -817,10 +814,10 @@
         <v>11.6</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>95.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>25.8</v>
@@ -840,17 +837,17 @@
       <c r="V4" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+      <c r="X4" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y4" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z4" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -925,17 +922,17 @@
       <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>2.9</v>
+      <c r="W5" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X5" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="Z5" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -966,7 +963,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -1057,7 +1054,7 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.1</v>
+        <v>1.9</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0</v>
@@ -1095,17 +1092,17 @@
       <c r="V7" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>4.1</v>
+      <c r="X7" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="Z7" s="9" t="n">
+        <v>2.7</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1139,7 +1136,7 @@
         <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
@@ -1180,17 +1177,17 @@
       <c r="V8" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>2.6</v>
+      <c r="X8" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="Z8" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1206,7 +1203,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>174.7</v>
+        <v>174.9</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>128.9</v>
@@ -1233,7 +1230,7 @@
         <v>7.7</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>57.2</v>
+        <v>56.7</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>55.2</v>
@@ -1252,7 +1249,7 @@
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1263,14 +1260,14 @@
       <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="15" t="n">
+      <c r="W9" s="9" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>14.5</v>
+        <v>414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1332,30 +1329,32 @@
         <v>20.3</v>
       </c>
       <c r="R10" s="9" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S10" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T10" s="9" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="U10" s="9" t="n">
-        <v>4.3</v>
+        <v>16.1</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>6.7</v>
       </c>
       <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="15" t="n">
+      <c r="W10" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="X10" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="Z10" s="9" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1370,7 +1369,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.5</v>
+        <v>509.3</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>27.3</v>
@@ -1393,7 +1392,7 @@
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
@@ -1415,31 +1414,31 @@
         <v>26.3</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>12.4</v>
+        <v>17.1</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>14.4</v>
+        <v>19.5</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>42</v>
+        <v>56.9</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>19.9</v>
+        <v>14.7</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X11" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="9" t="n">
-        <v>20.1</v>
-      </c>
       <c r="Y11" s="9" t="n">
-        <v>75.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="Z11" s="9" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1478,7 +1477,7 @@
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1514,17 +1513,17 @@
       <c r="V12" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="9" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="X12" s="9" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Y12" s="9" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z12" s="9" t="n">
-        <v>8.6</v>
+      <c r="W12" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1558,12 +1557,12 @@
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
@@ -1579,7 +1578,7 @@
         <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>18.9</v>
@@ -1646,13 +1645,13 @@
         <v>1.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>6.7</v>
+        <v>11.5</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>16.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13</v>
@@ -1684,17 +1683,17 @@
       <c r="V14" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="9" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X14" s="9" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="Y14" s="9" t="n">
-        <v>104.6</v>
-      </c>
-      <c r="Z14" s="9" t="n">
-        <v>-0.8</v>
+      <c r="W14" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1710,7 +1709,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>31</v>
+        <v>631</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>26</v>
@@ -1733,7 +1732,7 @@
       <c r="J15" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1799,12 +1798,12 @@
         <v>128</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>56.8</v>
+        <v>57</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="3" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1816,20 +1815,20 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="15" t="n">
+      <c r="K16" s="9" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="15" t="n">
+      <c r="L16" s="14" t="n">
         <v>59.1</v>
       </c>
-      <c r="M16" s="15" t="n">
+      <c r="M16" s="14" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
@@ -1852,8 +1851,8 @@
       <c r="V16" s="9" t="n">
         <v>98.2</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>78.7</v>
+      <c r="W16" s="14" t="n">
+        <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
@@ -1899,13 +1898,13 @@
         <v>2.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>27.4</v>
+        <v>29.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="15" t="n">
+      <c r="L17" s="14" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="15" t="n">
+      <c r="M17" s="14" t="n">
         <v>11.6</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1915,7 +1914,7 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>22.2</v>
@@ -1935,17 +1934,17 @@
       <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="14" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="Y17" s="9" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="Z17" s="9" t="n">
-        <v>4.5</v>
+      <c r="X17" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1979,7 +1978,7 @@
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -2170,7 +2169,7 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>28</v>
@@ -2237,22 +2236,22 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>13.1</v>
+        <v>17.6</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>13</v>
+        <v>17.4</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>14.9</v>
+        <v>19.9</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>98.7</v>
+        <v>99</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>0.2</v>
@@ -2301,13 +2300,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9</v>
+        <v>429</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>18.7</v>
@@ -2404,7 +2403,7 @@
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>20.8</v>
@@ -2413,19 +2412,19 @@
         <v>0.3</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="M23" s="15" t="n">
+        <v>67</v>
+      </c>
+      <c r="M23" s="14" t="n">
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>93</v>
+        <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>128.9</v>
@@ -2492,19 +2491,19 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>22.1</v>
+        <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="15" t="n">
+      <c r="M24" s="14" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2574,10 +2573,10 @@
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
@@ -2662,7 +2661,7 @@
         <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0.9</v>
@@ -2701,10 +2700,10 @@
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>25.5</v>
+        <v>13.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>14.2</v>
+        <v>142.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>55</v>
@@ -2747,7 +2746,7 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>7.1</v>
@@ -2817,13 +2816,13 @@
         <v>27</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.1</v>
@@ -2907,8 +2906,8 @@
       <c r="F29" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="9" t="n">
-        <v>18.7</v>
+      <c r="G29" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2941,16 +2940,16 @@
         <v>27</v>
       </c>
       <c r="R29" s="9" t="n">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="S29" s="9" t="n">
-        <v>17</v>
+        <v>21.6</v>
       </c>
       <c r="T29" s="9" t="n">
-        <v>47.8</v>
+        <v>60.4</v>
       </c>
       <c r="U29" s="9" t="n">
-        <v>18.6</v>
+        <v>14.1</v>
       </c>
       <c r="V29" s="9" t="n">
         <v>22.8</v>
@@ -2981,7 +2980,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>228.4</v>
+        <v>2284.8</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>131.2</v>
@@ -2996,7 +2995,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -3032,7 +3031,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>14.8</v>
+        <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>55.4</v>
@@ -3040,7 +3039,7 @@
       <c r="V30" s="9" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="15" t="n">
+      <c r="W30" s="14" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3096,8 +3095,8 @@
       <c r="M31" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>12.4</v>
+      <c r="N31" s="9" t="n">
+        <v>13.2</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3123,7 +3122,7 @@
       <c r="V31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="15" t="n">
+      <c r="W31" s="14" t="n">
         <v>16.4</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3133,7 +3132,7 @@
         <v>730.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>25.8</v>
+        <v>165.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3194,7 +3193,7 @@
         <v>21.1</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
@@ -3332,7 +3331,7 @@
         <v>8.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.5</v>
@@ -3347,10 +3346,10 @@
         <v>16</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="O34" s="9" t="n">
         <v>99</v>
@@ -3453,7 +3452,7 @@
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
@@ -3541,7 +3540,7 @@
         <v>45</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17.2</v>
+        <v>17.9</v>
       </c>
       <c r="V36" s="9" t="n">
         <v>20.6</v>
@@ -3572,7 +3571,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>224.4</v>
+        <v>224</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>128.5</v>
@@ -3587,7 +3586,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>14.1</v>
@@ -3608,20 +3607,20 @@
         <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>92</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="15" t="n">
+      <c r="Q37" s="14" t="n">
         <v>115.5</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>88.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>16.4</v>
+        <v>316.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
@@ -3633,7 +3632,7 @@
         <v>83.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.7</v>
+        <v>82.7</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
@@ -3676,7 +3675,7 @@
         <v>28.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>42.1</v>
+        <v>22.1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
@@ -3696,7 +3695,7 @@
       <c r="P38" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="15" t="n">
+      <c r="Q38" s="14" t="n">
         <v>23.1</v>
       </c>
       <c r="R38" s="9" t="n">
@@ -3709,7 +3708,7 @@
         <v>63.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="V38" s="9" t="n">
         <v>20.2</v>
@@ -3743,7 +3742,7 @@
         <v>579.9</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
       <c r="E39" s="9" t="n">
         <v>11</v>
@@ -3755,7 +3754,7 @@
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.5</v>
@@ -3769,30 +3768,32 @@
       <c r="L39" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q39" s="3" t="n">
+      <c r="N39" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P39" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q39" s="9" t="n">
         <v>26.6</v>
       </c>
       <c r="R39" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>19</v>
+      <c r="S39" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="T39" s="9" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>14.2</v>
       </c>
       <c r="V39" s="9" t="n">
         <v>21.7</v>
@@ -3856,13 +3857,13 @@
         <v>10.3</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>98.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>22</v>
@@ -3923,7 +3924,7 @@
         <v>19.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>3.6</v>
@@ -3937,32 +3938,32 @@
       <c r="L41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+      <c r="N41" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="O41" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P41" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q41" s="9" t="n">
         <v>23.4</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>12.9</v>
+      <c r="S41" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="T41" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>8.9</v>
       </c>
       <c r="V41" s="9" t="n">
         <v>22</v>
@@ -4022,32 +4023,32 @@
       <c r="L42" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q42" s="14" t="n">
-        <v>2.6</v>
+      <c r="M42" s="9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="N42" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="P42" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q42" s="9" t="n">
+        <v>26.6</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>19.6</v>
+      <c r="S42" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T42" s="9" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="U42" s="9" t="n">
+        <v>14.7</v>
       </c>
       <c r="V42" s="9" t="n">
         <v>22</v>
@@ -4081,11 +4082,11 @@
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="13" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="13" t="inlineStr"/>
+      <c r="Q43" s="9" t="inlineStr"/>
       <c r="R43" s="9" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
@@ -4120,11 +4121,11 @@
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="13" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="13" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr"/>
       <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
@@ -4160,10 +4161,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>27.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>14.4</v>
@@ -4177,19 +4178,19 @@
       <c r="L45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="15" t="n">
+      <c r="M45" s="9" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>5.1</v>
+        <v>51.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q45" s="15" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q45" s="9" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="R45" s="9" t="n">
@@ -4254,18 +4255,18 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.2</v>
+        <v>52.1</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>111100</v>
+        <v>101.1</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="M46" s="15" t="n">
+      <c r="M46" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="N46" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
@@ -4274,20 +4275,20 @@
       <c r="P46" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q46" s="15" t="n">
+      <c r="Q46" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>14.7</v>
+      <c r="S46" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="T46" s="9" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="U46" s="9" t="n">
+        <v>10.9</v>
       </c>
       <c r="V46" s="9" t="n">
         <v>21.3</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalcmultiday.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalcmultiday.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,22 +143,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -780,16 +771,16 @@
       <c r="C4" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -801,53 +792,53 @@
       <c r="J4" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="K4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M4" s="9" t="n">
+      <c r="L4" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M4" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="O4" s="9" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="P4" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q4" s="9" t="n">
+      <c r="O4" s="8" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q4" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="8" t="n">
         <v>42.5</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y4" s="9" t="n">
-        <v>79</v>
-      </c>
-      <c r="Z4" s="9" t="n">
-        <v>5.6</v>
+      <c r="X4" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -865,16 +856,16 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -886,53 +877,53 @@
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="N5" s="9" t="n">
+      <c r="N5" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="O5" s="9" t="n">
+      <c r="O5" s="8" t="n">
         <v>94.2</v>
       </c>
-      <c r="P5" s="9" t="n">
+      <c r="P5" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="S5" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="T5" s="9" t="n">
+      <c r="T5" s="8" t="n">
         <v>94</v>
       </c>
-      <c r="U5" s="9" t="n">
+      <c r="U5" s="8" t="n">
         <v>1.4</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X5" s="9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y5" s="9" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="Z5" s="9" t="n">
-        <v>3</v>
+      <c r="W5" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -950,16 +941,16 @@
       <c r="C6" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -971,52 +962,52 @@
       <c r="J6" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="9" t="n">
+      <c r="N6" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="O6" s="9" t="n">
+      <c r="O6" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P6" s="9" t="n">
+      <c r="P6" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="S6" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="T6" s="9" t="n">
+      <c r="T6" s="8" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="X6" s="9" t="n">
+      <c r="X6" s="8" t="n">
         <v>17.1</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="Y6" s="8" t="n">
         <v>95</v>
       </c>
-      <c r="Z6" s="9" t="n">
+      <c r="Z6" s="8" t="n">
         <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1035,16 +1026,16 @@
       <c r="C7" s="3" t="n">
         <v>275.8</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>9</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1054,55 +1045,55 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K7" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="8" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="N7" s="9" t="n">
+      <c r="N7" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="O7" s="9" t="n">
+      <c r="O7" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P7" s="9" t="n">
+      <c r="P7" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="S7" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="T7" s="8" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="U7" s="9" t="n">
+      <c r="U7" s="8" t="n">
         <v>3.3</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="9" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y7" s="9" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="Z7" s="9" t="n">
-        <v>2.7</v>
+      <c r="X7" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1120,74 +1111,74 @@
       <c r="C8" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="N8" s="9" t="n">
+      <c r="N8" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="O8" s="9" t="n">
+      <c r="O8" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P8" s="9" t="n">
+      <c r="P8" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="S8" s="9" t="n">
+      <c r="S8" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="T8" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="U8" s="9" t="n">
+      <c r="U8" s="8" t="n">
         <v>4.3</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="X8" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Y8" s="9" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="Z8" s="9" t="n">
-        <v>1.8</v>
+      <c r="X8" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1203,18 +1194,18 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D9" s="8" t="n">
         <v>128.9</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1226,13 +1217,13 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="8" t="n">
         <v>7.7</v>
       </c>
-      <c r="L9" s="9" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="M9" s="9" t="n">
+      <c r="L9" s="8" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="M9" s="8" t="n">
         <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1242,14 +1233,14 @@
         <v>484.9</v>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="8" t="n">
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.3</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1257,10 +1248,10 @@
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="13" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1288,16 +1279,16 @@
       <c r="C10" s="3" t="n">
         <v>349.9</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1310,51 +1301,49 @@
         <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="O10" s="9" t="n">
+      <c r="O10" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P10" s="9" t="n">
+      <c r="P10" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="V10" s="9" t="n">
+      <c r="R10" s="8" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V10" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="9" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y10" s="9" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="Z10" s="9" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="X10" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="Z10" s="3" t="inlineStr"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1369,18 +1358,18 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.3</v>
-      </c>
-      <c r="D11" s="9" t="n">
+        <v>504.5</v>
+      </c>
+      <c r="D11" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -1392,14 +1381,14 @@
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1410,34 +1399,34 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="R11" s="9" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S11" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T11" s="9" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="U11" s="9" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V11" s="9" t="n">
+      <c r="R11" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="X11" s="9" t="n">
+      <c r="X11" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="Y11" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="Z11" s="9" t="n">
+      <c r="Z11" s="8" t="n">
         <v>9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1456,16 +1445,16 @@
       <c r="C12" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1477,7 +1466,7 @@
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1495,26 +1484,26 @@
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="R12" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S12" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T12" s="9" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="V12" s="9" t="n">
+      <c r="R12" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V12" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.7</v>
+        <v>14.7</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>13.1</v>
@@ -1541,35 +1530,35 @@
       <c r="C13" s="3" t="n">
         <v>357.9</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>11.6</v>
+        <v>18.6</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>13.6</v>
@@ -1580,34 +1569,34 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="T13" s="8" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" s="8" t="n">
         <v>2.1</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X13" s="9" t="n">
+      <c r="X13" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="Y13" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="Z13" s="9" t="n">
+      <c r="Z13" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -1626,16 +1615,16 @@
       <c r="C14" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1645,13 +1634,13 @@
         <v>1.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>16.7</v>
+        <v>8.5</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>23.2</v>
+        <v>13.3</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13</v>
@@ -1665,22 +1654,22 @@
       <c r="P14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="S14" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="T14" s="9" t="n">
+      <c r="T14" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="U14" s="9" t="n">
+      <c r="U14" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1711,16 +1700,16 @@
       <c r="C15" s="3" t="n">
         <v>631</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1732,7 +1721,7 @@
       <c r="J15" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1750,34 +1739,34 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="S15" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="T15" s="9" t="n">
+      <c r="T15" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="X15" s="9" t="n">
+      <c r="X15" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="Y15" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="Z15" s="9" t="n">
+      <c r="Z15" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -1794,13 +1783,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="8" t="n">
         <v>92.5</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1815,13 +1804,13 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="13" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="14" t="n">
+      <c r="L16" s="13" t="n">
         <v>59.1</v>
       </c>
-      <c r="M16" s="14" t="n">
+      <c r="M16" s="13" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1833,10 +1822,10 @@
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>111</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="R16" s="8" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1848,10 +1837,10 @@
       <c r="U16" s="3" t="n">
         <v>60.9</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="8" t="n">
         <v>98.2</v>
       </c>
-      <c r="W16" s="14" t="n">
+      <c r="W16" s="13" t="n">
         <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1879,16 +1868,16 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1901,10 +1890,10 @@
         <v>29.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="14" t="n">
+      <c r="L17" s="13" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="13" t="n">
         <v>11.6</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1914,27 +1903,27 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="S17" s="9" t="n">
+      <c r="S17" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="T17" s="9" t="n">
+      <c r="T17" s="8" t="n">
         <v>69.7</v>
       </c>
-      <c r="U17" s="9" t="n">
+      <c r="U17" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="14" t="n">
+      <c r="W17" s="13" t="n">
         <v>16.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1944,7 +1933,7 @@
         <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1962,73 +1951,73 @@
       <c r="C18" s="3" t="n">
         <v>45.5</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="8" t="n">
         <v>14.5</v>
       </c>
-      <c r="N18" s="9" t="n">
+      <c r="N18" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="O18" s="9" t="n">
+      <c r="O18" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P18" s="9" t="n">
+      <c r="P18" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="9" t="n">
+      <c r="Q18" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="S18" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="T18" s="8" t="n">
         <v>46.2</v>
       </c>
-      <c r="U18" s="9" t="n">
+      <c r="U18" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="9" t="n">
+      <c r="X18" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="Y18" s="9" t="n">
+      <c r="Y18" s="8" t="n">
         <v>70.8</v>
       </c>
-      <c r="Z18" s="9" t="n">
+      <c r="Z18" s="8" t="n">
         <v>7.3</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2047,16 +2036,16 @@
       <c r="C19" s="3" t="n">
         <v>531.1</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2068,10 +2057,10 @@
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2086,34 +2075,34 @@
       <c r="P19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="T19" s="9" t="n">
+      <c r="T19" s="8" t="n">
         <v>48.5</v>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="X19" s="9" t="n">
+      <c r="X19" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y19" s="9" t="n">
+      <c r="Y19" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="Z19" s="9" t="n">
+      <c r="Z19" s="8" t="n">
         <v>6.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -2132,16 +2121,16 @@
       <c r="C20" s="3" t="n">
         <v>542.2</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2153,10 +2142,10 @@
       <c r="J20" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2169,36 +2158,36 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q20" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q20" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="S20" s="9" t="n">
+      <c r="S20" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="T20" s="9" t="n">
+      <c r="T20" s="8" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="9" t="n">
+      <c r="U20" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="X20" s="9" t="n">
+      <c r="X20" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="Y20" s="9" t="n">
+      <c r="Y20" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="Z20" s="9" t="n">
+      <c r="Z20" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -2215,18 +2204,18 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>382.4</v>
-      </c>
-      <c r="D21" s="9" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2236,54 +2225,54 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K21" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="N21" s="9" t="n">
+      <c r="N21" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="O21" s="9" t="n">
+      <c r="O21" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P21" s="9" t="n">
+      <c r="P21" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="S21" s="9" t="n">
+      <c r="S21" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="T21" s="9" t="n">
+      <c r="T21" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="9" t="n">
+      <c r="U21" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="n">
         <v>17.5</v>
       </c>
-      <c r="X21" s="9" t="n">
+      <c r="X21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="Y21" s="9" t="n">
+      <c r="Y21" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="Z21" s="9" t="n">
+      <c r="Z21" s="8" t="n">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2300,18 +2289,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>429</v>
-      </c>
-      <c r="D22" s="9" t="n">
+        <v>309</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2323,52 +2312,52 @@
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="N22" s="9" t="n">
+      <c r="N22" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" s="8" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="P22" s="9" t="n">
+      <c r="P22" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="S22" s="9" t="n">
+      <c r="S22" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="T22" s="9" t="n">
+      <c r="T22" s="8" t="n">
         <v>49.5</v>
       </c>
-      <c r="U22" s="9" t="n">
+      <c r="U22" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="9" t="n">
+      <c r="X22" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="Y22" s="9" t="n">
+      <c r="Y22" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="Z22" s="9" t="n">
+      <c r="Z22" s="8" t="n">
         <v>9.5</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -2385,18 +2374,18 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2320.3</v>
-      </c>
-      <c r="D23" s="9" t="n">
+        <v>232</v>
+      </c>
+      <c r="D23" s="8" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>56.7</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2408,13 +2397,13 @@
       <c r="J23" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="9" t="n">
+      <c r="L23" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="M23" s="14" t="n">
+      <c r="M23" s="13" t="n">
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2424,12 +2413,12 @@
         <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q23" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q23" s="8" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="8" t="n">
         <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2441,10 +2430,10 @@
       <c r="U23" s="3" t="n">
         <v>88.5</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="8" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2472,16 +2461,16 @@
       <c r="C24" s="3" t="n">
         <v>464.1</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2494,16 +2483,16 @@
         <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="14" t="n">
+      <c r="M24" s="13" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.8</v>
+        <v>10.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2511,34 +2500,34 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="9" t="n">
+      <c r="S24" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="T24" s="9" t="n">
+      <c r="T24" s="8" t="n">
         <v>60.5</v>
       </c>
-      <c r="U24" s="9" t="n">
+      <c r="U24" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="8" t="n">
         <v>17.1</v>
       </c>
-      <c r="X24" s="9" t="n">
+      <c r="X24" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="Y24" s="9" t="n">
+      <c r="Y24" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="Z24" s="9" t="n">
+      <c r="Z24" s="8" t="n">
         <v>5.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -2557,16 +2546,16 @@
       <c r="C25" s="3" t="n">
         <v>488.9</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2578,52 +2567,52 @@
       <c r="J25" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="9" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="N25" s="9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="O25" s="9" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="P25" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q25" s="9" t="n">
+      <c r="K25" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q25" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="S25" s="9" t="n">
+      <c r="S25" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="T25" s="9" t="n">
+      <c r="T25" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="U25" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="X25" s="9" t="n">
+      <c r="X25" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="Y25" s="9" t="n">
+      <c r="Y25" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="Z25" s="9" t="n">
+      <c r="Z25" s="8" t="n">
         <v>8.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -2642,16 +2631,16 @@
       <c r="C26" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>9.6</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
@@ -2663,53 +2652,53 @@
       <c r="J26" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="N26" s="9" t="n">
+      <c r="N26" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="O26" s="9" t="n">
+      <c r="O26" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P26" s="9" t="n">
+      <c r="P26" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="S26" s="9" t="n">
+      <c r="S26" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="T26" s="9" t="n">
+      <c r="T26" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="U26" s="9" t="n">
+      <c r="U26" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>142.2</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>11.8</v>
+      <c r="W26" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y26" s="8" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="Z26" s="8" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2727,16 +2716,16 @@
       <c r="C27" s="3" t="n">
         <v>340.2</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="8" t="n">
         <v>25.1</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="8" t="n">
         <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2748,53 +2737,53 @@
       <c r="J27" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="N27" s="9" t="n">
+      <c r="N27" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="O27" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="S27" s="9" t="n">
+      <c r="S27" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="T27" s="9" t="n">
+      <c r="T27" s="8" t="n">
         <v>90.3</v>
       </c>
-      <c r="U27" s="9" t="n">
+      <c r="U27" s="8" t="n">
         <v>1.9</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="X27" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>1.6</v>
+      <c r="X27" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y27" s="8" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="Z27" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2812,16 +2801,16 @@
       <c r="C28" s="3" t="n">
         <v>513.3</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2833,53 +2822,53 @@
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="N28" s="9" t="n">
+      <c r="N28" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="O28" s="9" t="n">
+      <c r="O28" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P28" s="9" t="n">
+      <c r="P28" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="S28" s="9" t="n">
+      <c r="S28" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="T28" s="9" t="n">
+      <c r="T28" s="8" t="n">
         <v>76.7</v>
       </c>
-      <c r="U28" s="9" t="n">
+      <c r="U28" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>1.8</v>
+      <c r="X28" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y28" s="8" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="Z28" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2897,17 +2886,17 @@
       <c r="C29" s="3" t="n">
         <v>593.3</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2918,52 +2907,52 @@
       <c r="J29" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="8" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="P29" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="S29" s="9" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="T29" s="9" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="U29" s="9" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="V29" s="9" t="n">
+      <c r="R29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="V29" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="X29" s="9" t="n">
+      <c r="X29" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="Y29" s="9" t="n">
+      <c r="Y29" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="Z29" s="9" t="n">
+      <c r="Z29" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -2980,22 +2969,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="D30" s="8" t="n">
         <v>131.2</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>52.1</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="8" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -3003,13 +2992,13 @@
       <c r="J30" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="13" t="n">
         <v>13.5</v>
       </c>
-      <c r="L30" s="9" t="n">
+      <c r="L30" s="8" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="8" t="n">
         <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3021,10 +3010,10 @@
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="8" t="n">
         <v>113.2</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="8" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3036,10 +3025,10 @@
       <c r="U30" s="3" t="n">
         <v>55.4</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="8" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="14" t="n">
+      <c r="W30" s="8" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3067,16 +3056,16 @@
       <c r="C31" s="3" t="n">
         <v>457</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3089,14 +3078,14 @@
         <v>3.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M31" s="9" t="n">
+      <c r="L31" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M31" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="9" t="n">
-        <v>13.2</v>
+      <c r="N31" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3104,35 +3093,35 @@
       <c r="P31" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="S31" s="9" t="n">
+      <c r="S31" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="U31" s="9" t="n">
+      <c r="U31" s="8" t="n">
         <v>7.7</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="14" t="n">
+      <c r="W31" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>730.2</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>165.8</v>
+      <c r="X31" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y31" s="8" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="Z31" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3150,16 +3139,16 @@
       <c r="C32" s="3" t="n">
         <v>520</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
@@ -3171,50 +3160,50 @@
       <c r="J32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="9" t="n">
+      <c r="K32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="N32" s="9" t="n">
+      <c r="N32" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="O32" s="9" t="n">
+      <c r="O32" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P32" s="9" t="n">
+      <c r="P32" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>62.2</v>
+        <v>62.5</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="W32" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="9" t="n">
+      <c r="X32" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="Y32" s="9" t="n">
+      <c r="Y32" s="8" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="Z32" s="9" t="n">
+      <c r="Z32" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -3233,16 +3222,16 @@
       <c r="C33" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3254,28 +3243,28 @@
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="8" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="9" t="n">
+      <c r="L33" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="N33" s="9" t="n">
+      <c r="N33" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="O33" s="9" t="n">
+      <c r="O33" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P33" s="9" t="n">
+      <c r="P33" s="8" t="n">
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3287,19 +3276,19 @@
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V33" s="9" t="n">
+      <c r="V33" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="X33" s="9" t="n">
+      <c r="X33" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="Y33" s="9" t="n">
+      <c r="Y33" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="Z33" s="9" t="n">
+      <c r="Z33" s="8" t="n">
         <v>2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -3318,16 +3307,16 @@
       <c r="C34" s="3" t="n">
         <v>329.1</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>8.6</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3339,28 +3328,28 @@
       <c r="J34" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="8" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="N34" s="9" t="n">
+      <c r="N34" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="O34" s="9" t="n">
+      <c r="O34" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P34" s="9" t="n">
+      <c r="P34" s="8" t="n">
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3372,19 +3361,19 @@
       <c r="U34" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="9" t="n">
+      <c r="X34" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y34" s="9" t="n">
+      <c r="Y34" s="8" t="n">
         <v>88.7</v>
       </c>
-      <c r="Z34" s="9" t="n">
+      <c r="Z34" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -3403,16 +3392,16 @@
       <c r="C35" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>14</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3424,52 +3413,52 @@
       <c r="J35" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="N35" s="9" t="n">
+      <c r="N35" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="O35" s="9" t="n">
+      <c r="O35" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P35" s="9" t="n">
+      <c r="P35" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="9" t="n">
+      <c r="V35" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="X35" s="9" t="n">
+      <c r="X35" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="Y35" s="9" t="n">
+      <c r="Y35" s="8" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="Z35" s="9" t="n">
+      <c r="Z35" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -3488,16 +3477,16 @@
       <c r="C36" s="3" t="n">
         <v>535.5</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3509,52 +3498,52 @@
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="N36" s="9" t="n">
+      <c r="N36" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="O36" s="9" t="n">
+      <c r="O36" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P36" s="9" t="n">
+      <c r="P36" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>17.1</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="X36" s="9" t="n">
+      <c r="X36" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="Y36" s="9" t="n">
+      <c r="Y36" s="8" t="n">
         <v>68.5</v>
       </c>
-      <c r="Z36" s="9" t="n">
+      <c r="Z36" s="8" t="n">
         <v>7.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -3573,16 +3562,16 @@
       <c r="C37" s="3" t="n">
         <v>224</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>128.5</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="8" t="n">
         <v>60.9</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G37" s="8" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
@@ -3594,13 +3583,13 @@
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="8" t="n">
         <v>8.5</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="8" t="n">
         <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3610,10 +3599,10 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="14" t="n">
+      <c r="Q37" s="13" t="n">
         <v>115.5</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="8" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3625,14 +3614,14 @@
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" s="8" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="8" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>82.7</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
@@ -3656,23 +3645,23 @@
       <c r="C38" s="3" t="n">
         <v>448.1</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>28.1</v>
+        <v>2.8</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>22.1</v>
@@ -3680,25 +3669,25 @@
       <c r="K38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="N38" s="9" t="n">
+      <c r="N38" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="O38" s="9" t="n">
+      <c r="O38" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P38" s="9" t="n">
+      <c r="P38" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="14" t="n">
+      <c r="Q38" s="13" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3710,19 +3699,19 @@
       <c r="U38" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="9" t="n">
+      <c r="X38" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="Y38" s="9" t="n">
+      <c r="Y38" s="8" t="n">
         <v>79.8</v>
       </c>
-      <c r="Z38" s="9" t="n">
+      <c r="Z38" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -3741,16 +3730,16 @@
       <c r="C39" s="3" t="n">
         <v>579.9</v>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="E39" s="9" t="n">
+      <c r="D39" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E39" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
@@ -3762,52 +3751,52 @@
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="9" t="n">
+      <c r="N39" s="8" t="n">
         <v>14.5</v>
       </c>
-      <c r="O39" s="9" t="n">
+      <c r="O39" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P39" s="9" t="n">
+      <c r="P39" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="R39" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="S39" s="9" t="n">
+      <c r="S39" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="T39" s="9" t="n">
+      <c r="T39" s="8" t="n">
         <v>59.2</v>
       </c>
-      <c r="U39" s="9" t="n">
+      <c r="U39" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="V39" s="9" t="n">
+      <c r="V39" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="X39" s="9" t="n">
+      <c r="X39" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="Y39" s="9" t="n">
+      <c r="Y39" s="8" t="n">
         <v>68.7</v>
       </c>
-      <c r="Z39" s="9" t="n">
+      <c r="Z39" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -3826,13 +3815,13 @@
       <c r="C40" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3847,52 +3836,52 @@
       <c r="J40" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="8" t="n">
         <v>10.3</v>
       </c>
-      <c r="N40" s="9" t="n">
+      <c r="N40" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="O40" s="9" t="n">
+      <c r="O40" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P40" s="9" t="n">
+      <c r="P40" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="S40" s="9" t="n">
+      <c r="S40" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="T40" s="9" t="n">
+      <c r="T40" s="8" t="n">
         <v>69.5</v>
       </c>
-      <c r="U40" s="9" t="n">
+      <c r="U40" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="V40" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="9" t="n">
+      <c r="X40" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y40" s="9" t="n">
+      <c r="Y40" s="8" t="n">
         <v>83.3</v>
       </c>
-      <c r="Z40" s="9" t="n">
+      <c r="Z40" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -3911,16 +3900,16 @@
       <c r="C41" s="3" t="n">
         <v>451.2</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3932,52 +3921,52 @@
       <c r="J41" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N41" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="O41" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P41" s="9" t="n">
+      <c r="P41" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="9" t="n">
+      <c r="S41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T41" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="U41" s="9" t="n">
+      <c r="U41" s="8" t="n">
         <v>8.9</v>
       </c>
-      <c r="V41" s="9" t="n">
+      <c r="V41" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="X41" s="9" t="n">
+      <c r="X41" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="Y41" s="9" t="n">
+      <c r="Y41" s="8" t="n">
         <v>80.5</v>
       </c>
-      <c r="Z41" s="9" t="n">
+      <c r="Z41" s="8" t="n">
         <v>5.1</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -3996,16 +3985,16 @@
       <c r="C42" s="3" t="n">
         <v>524.4</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4017,43 +4006,43 @@
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="8" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="S42" s="9" t="n">
+      <c r="S42" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="8" t="n">
         <v>57.7</v>
       </c>
-      <c r="U42" s="9" t="n">
+      <c r="U42" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="9" t="inlineStr"/>
+      <c r="W42" s="8" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -4071,28 +4060,28 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="8" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="9" t="inlineStr"/>
-      <c r="R43" s="9" t="inlineStr"/>
+      <c r="Q43" s="8" t="inlineStr"/>
+      <c r="R43" s="8" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="9" t="inlineStr"/>
-      <c r="W43" s="9" t="inlineStr"/>
+      <c r="V43" s="8" t="inlineStr"/>
+      <c r="W43" s="8" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4110,28 +4099,28 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="9" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="9" t="inlineStr"/>
-      <c r="W44" s="9" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4149,22 +4138,22 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1911.2</v>
-      </c>
-      <c r="D45" s="9" t="n">
+        <v>191.1</v>
+      </c>
+      <c r="D45" s="8" t="n">
         <v>109.7</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="8" t="n">
         <v>41.5</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="8" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>14.4</v>
@@ -4172,13 +4161,13 @@
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="9" t="n">
+      <c r="L45" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="8" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4188,12 +4177,12 @@
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="Q45" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q45" s="8" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="8" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4205,14 +4194,14 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" s="8" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="W45" s="9" t="n">
+      <c r="W45" s="8" t="n">
         <v>51</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>66.8</v>
+        <v>60.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4236,16 +4225,16 @@
       <c r="C46" s="3" t="n">
         <v>477.8</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4255,18 +4244,18 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="K46" s="8" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="L46" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="9" t="n">
+      <c r="N46" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
@@ -4275,34 +4264,34 @@
       <c r="P46" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="9" t="n">
+      <c r="S46" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="T46" s="9" t="n">
+      <c r="T46" s="8" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="U46" s="9" t="n">
+      <c r="U46" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X46" s="9" t="n">
+      <c r="X46" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y46" s="9" t="n">
+      <c r="Y46" s="8" t="n">
         <v>75.5</v>
       </c>
-      <c r="Z46" s="9" t="n">
+      <c r="Z46" s="8" t="n">
         <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalcmultiday.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_recalcmultiday.xlsx
@@ -146,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -802,19 +802,19 @@
         <v>9.1</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>95.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="S4" s="8" t="n">
         <v>14.1</v>
@@ -887,13 +887,13 @@
         <v>11.4</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>94.2</v>
+        <v>90</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>19.6</v>
@@ -902,13 +902,13 @@
         <v>18.6</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="V5" s="8" t="n">
         <v>19.5</v>
@@ -975,10 +975,10 @@
         <v>13.1</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" s="8" t="n">
         <v>15.4</v>
@@ -987,22 +987,22 @@
         <v>14.7</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>95.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="V6" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="Y6" s="8" t="n">
         <v>95</v>
@@ -1057,13 +1057,13 @@
         <v>13.1</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" s="8" t="n">
         <v>19.3</v>
@@ -1072,27 +1072,27 @@
         <v>16.8</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>19.1</v>
+        <v>17.4</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>85.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="V7" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z7" s="3" t="n">
+      <c r="X7" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y7" s="8" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="Z7" s="8" t="n">
         <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1142,13 +1142,13 @@
         <v>10.6</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>98.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q8" s="8" t="n">
         <v>21.4</v>
@@ -1157,27 +1157,27 @@
         <v>18.4</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>21.2</v>
+        <v>19.1</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="V8" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="Z8" s="3" t="n">
+      <c r="X8" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y8" s="8" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="Z8" s="8" t="n">
         <v>2.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1308,13 +1308,13 @@
         <v>11</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>98</v>
+        <v>96.5</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q10" s="8" t="n">
         <v>20.3</v>
@@ -1323,13 +1323,13 @@
         <v>17.1</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>81.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="V10" s="8" t="n">
         <v>19</v>
@@ -1403,7 +1403,7 @@
         <v>26.3</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>12.4</v>
+        <v>17.1</v>
       </c>
       <c r="S11" s="8" t="n">
         <v>14.4</v>
@@ -1417,8 +1417,8 @@
       <c r="V11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>15.5</v>
+      <c r="W11" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="X11" s="8" t="n">
         <v>17.6</v>
@@ -1488,7 +1488,7 @@
         <v>25.4</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="S12" s="8" t="n">
         <v>12.1</v>
@@ -1576,19 +1576,19 @@
         <v>17.3</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>19.7</v>
+        <v>18.6</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>90.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="V13" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>16.8</v>
+      <c r="W13" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>19.1</v>
@@ -1661,13 +1661,13 @@
         <v>14.7</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>98.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="V14" s="8" t="n">
         <v>14.5</v>
@@ -1743,7 +1743,7 @@
         <v>25.5</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>13.7</v>
+        <v>17.6</v>
       </c>
       <c r="S15" s="8" t="n">
         <v>15.7</v>
@@ -1757,8 +1757,8 @@
       <c r="V15" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>14.4</v>
+      <c r="W15" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="X15" s="8" t="n">
         <v>16.4</v>
@@ -1912,13 +1912,13 @@
         <v>16.4</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>18.6</v>
+        <v>14.7</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>69.7</v>
+        <v>54.9</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>8.1</v>
+        <v>12.1</v>
       </c>
       <c r="V17" s="8" t="n">
         <v>19.6</v>
@@ -1978,8 +1978,8 @@
       <c r="L18" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>14.5</v>
+      <c r="M18" s="10" t="n">
+        <v>1.6</v>
       </c>
       <c r="N18" s="8" t="n">
         <v>16.5</v>
@@ -1994,7 +1994,7 @@
         <v>25.8</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>13.4</v>
+        <v>17.5</v>
       </c>
       <c r="S18" s="8" t="n">
         <v>15.4</v>
@@ -2012,13 +2012,13 @@
         <v>15.5</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>17.6</v>
+        <v>13.9</v>
       </c>
       <c r="Y18" s="8" t="n">
-        <v>70.8</v>
+        <v>55.7</v>
       </c>
       <c r="Z18" s="8" t="n">
-        <v>7.3</v>
+        <v>11</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2063,23 +2063,23 @@
       <c r="L19" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P19" s="3" t="n">
+      <c r="N19" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P19" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="Q19" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>14.2</v>
+        <v>18</v>
       </c>
       <c r="S19" s="8" t="n">
         <v>16.2</v>
@@ -2094,7 +2094,7 @@
         <v>21.2</v>
       </c>
       <c r="W19" s="8" t="n">
-        <v>16.4</v>
+        <v>17.8</v>
       </c>
       <c r="X19" s="8" t="n">
         <v>18.6</v>
@@ -2148,23 +2148,23 @@
       <c r="L20" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="3" t="n">
+      <c r="N20" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P20" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="8" t="n">
         <v>28</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>13.3</v>
+        <v>18.1</v>
       </c>
       <c r="S20" s="8" t="n">
         <v>15.3</v>
@@ -2182,13 +2182,13 @@
         <v>18.4</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>21.2</v>
+        <v>18.6</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>79.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2233,8 +2233,8 @@
       <c r="L21" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <v>17.4</v>
+      <c r="M21" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>19.9</v>
@@ -2249,7 +2249,7 @@
         <v>25.6</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>14.8</v>
+        <v>18.2</v>
       </c>
       <c r="S21" s="8" t="n">
         <v>16.8</v>
@@ -2264,7 +2264,7 @@
         <v>19.8</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="X21" s="8" t="n">
         <v>20</v>
@@ -2334,7 +2334,7 @@
         <v>23.6</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>12.4</v>
+        <v>16.2</v>
       </c>
       <c r="S22" s="8" t="n">
         <v>14.4</v>
@@ -2352,13 +2352,13 @@
         <v>15.6</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>17.7</v>
+        <v>13</v>
       </c>
       <c r="Y22" s="8" t="n">
-        <v>65</v>
+        <v>47.8</v>
       </c>
       <c r="Z22" s="8" t="n">
-        <v>9.5</v>
+        <v>14.2</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2488,16 +2488,16 @@
       <c r="L24" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="13" t="n">
+      <c r="M24" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="N24" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="P24" s="3" t="n">
+      <c r="N24" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="P24" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="Q24" s="8" t="n">
@@ -2507,13 +2507,13 @@
         <v>17.6</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>20.1</v>
+        <v>14.5</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>60.5</v>
+        <v>43.7</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>13.1</v>
+        <v>18.7</v>
       </c>
       <c r="V24" s="8" t="n">
         <v>21.3</v>
@@ -2522,13 +2522,13 @@
         <v>17.1</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>19.5</v>
+        <v>16.6</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>77</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>5.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>17</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>16.7</v>
+        <v>9.9</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>19</v>
@@ -2592,19 +2592,19 @@
         <v>17.2</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>19.6</v>
+        <v>14.5</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>63</v>
+        <v>46.6</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>11.5</v>
+        <v>16.6</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>14.8</v>
+        <v>16.9</v>
       </c>
       <c r="X25" s="8" t="n">
         <v>16.8</v>
@@ -2662,13 +2662,13 @@
         <v>10.2</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>98.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P26" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q26" s="8" t="n">
         <v>21</v>
@@ -2677,13 +2677,13 @@
         <v>16.2</v>
       </c>
       <c r="S26" s="8" t="n">
-        <v>18.4</v>
+        <v>15.1</v>
       </c>
       <c r="T26" s="8" t="n">
-        <v>74</v>
+        <v>60.9</v>
       </c>
       <c r="U26" s="8" t="n">
-        <v>6.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="V26" s="8" t="n">
         <v>21.6</v>
@@ -2692,13 +2692,13 @@
         <v>15.5</v>
       </c>
       <c r="X26" s="8" t="n">
-        <v>17.6</v>
+        <v>13.4</v>
       </c>
       <c r="Y26" s="8" t="n">
-        <v>68.2</v>
+        <v>52.1</v>
       </c>
       <c r="Z26" s="8" t="n">
-        <v>8.199999999999999</v>
+        <v>12.3</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2747,13 +2747,13 @@
         <v>12.2</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>98.7</v>
+        <v>97.8</v>
       </c>
       <c r="P27" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q27" s="8" t="n">
         <v>17.6</v>
@@ -2762,13 +2762,13 @@
         <v>16</v>
       </c>
       <c r="S27" s="8" t="n">
-        <v>18.2</v>
+        <v>17.1</v>
       </c>
       <c r="T27" s="8" t="n">
-        <v>90.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="U27" s="8" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="V27" s="8" t="n">
         <v>17.4</v>
@@ -2777,13 +2777,13 @@
         <v>16.7</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" s="8" t="n">
-        <v>95.7</v>
+        <v>93.3</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2832,13 +2832,13 @@
         <v>13.3</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q28" s="8" t="n">
         <v>22.9</v>
@@ -2847,13 +2847,13 @@
         <v>18.6</v>
       </c>
       <c r="S28" s="8" t="n">
-        <v>21.4</v>
+        <v>18.5</v>
       </c>
       <c r="T28" s="8" t="n">
-        <v>76.7</v>
+        <v>66.2</v>
       </c>
       <c r="U28" s="8" t="n">
-        <v>6.5</v>
+        <v>9.4</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>16.4</v>
@@ -2862,13 +2862,13 @@
         <v>15.5</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>17.6</v>
+        <v>17</v>
       </c>
       <c r="Y28" s="8" t="n">
-        <v>94.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Z28" s="8" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2917,19 +2917,19 @@
         <v>10.5</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>97.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="P29" s="8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="8" t="n">
         <v>27</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>17</v>
@@ -2944,7 +2944,7 @@
         <v>22.8</v>
       </c>
       <c r="W29" s="8" t="n">
-        <v>14.7</v>
+        <v>17.3</v>
       </c>
       <c r="X29" s="8" t="n">
         <v>16.7</v>
@@ -3100,13 +3100,13 @@
         <v>17.3</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>19.7</v>
+        <v>16.1</v>
       </c>
       <c r="T31" s="8" t="n">
-        <v>72</v>
+        <v>58.8</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>7.7</v>
+        <v>11.3</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>19.9</v>
@@ -3115,13 +3115,13 @@
         <v>16.4</v>
       </c>
       <c r="X31" s="8" t="n">
-        <v>18.6</v>
+        <v>16.3</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>80.3</v>
+        <v>70</v>
       </c>
       <c r="Z31" s="8" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3170,13 +3170,13 @@
         <v>10.2</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>98</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P32" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>21.1</v>
@@ -3198,13 +3198,13 @@
         <v>17.6</v>
       </c>
       <c r="X32" s="8" t="n">
-        <v>20.1</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" s="8" t="n">
-        <v>78.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="Z32" s="8" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3253,13 +3253,13 @@
         <v>14.7</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>98.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>20.3</v>
@@ -3283,13 +3283,13 @@
         <v>17.9</v>
       </c>
       <c r="X33" s="8" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y33" s="8" t="n">
-        <v>91</v>
+        <v>86.5</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>16</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="N34" s="8" t="n">
         <v>17.8</v>
@@ -3368,13 +3368,13 @@
         <v>16.8</v>
       </c>
       <c r="X34" s="8" t="n">
-        <v>19.1</v>
+        <v>17.8</v>
       </c>
       <c r="Y34" s="8" t="n">
-        <v>88.7</v>
+        <v>82.7</v>
       </c>
       <c r="Z34" s="8" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3423,13 +3423,13 @@
         <v>12.9</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
@@ -3453,13 +3453,13 @@
         <v>16.7</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>19</v>
+        <v>16.2</v>
       </c>
       <c r="Y35" s="8" t="n">
-        <v>77.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="Z35" s="8" t="n">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3508,13 +3508,13 @@
         <v>10.5</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
@@ -3538,13 +3538,13 @@
         <v>14.6</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>16.6</v>
+        <v>12.5</v>
       </c>
       <c r="Y36" s="8" t="n">
-        <v>68.5</v>
+        <v>51.7</v>
       </c>
       <c r="Z36" s="8" t="n">
-        <v>7.6</v>
+        <v>11.7</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3676,13 +3676,13 @@
         <v>12.8</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>98.7</v>
+        <v>97.8</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q38" s="13" t="n">
         <v>23.1</v>
@@ -3706,13 +3706,13 @@
         <v>16.6</v>
       </c>
       <c r="X38" s="8" t="n">
-        <v>18.9</v>
+        <v>16.4</v>
       </c>
       <c r="Y38" s="8" t="n">
-        <v>79.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Z38" s="8" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3761,13 +3761,13 @@
         <v>12.5</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>98.7</v>
+        <v>97.8</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q39" s="8" t="n">
         <v>26.6</v>
@@ -3776,13 +3776,13 @@
         <v>18</v>
       </c>
       <c r="S39" s="8" t="n">
-        <v>20.6</v>
+        <v>14.8</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>59.2</v>
+        <v>42.4</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>14.2</v>
+        <v>20.1</v>
       </c>
       <c r="V39" s="8" t="n">
         <v>21.7</v>
@@ -3791,13 +3791,13 @@
         <v>15.7</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>17.8</v>
+        <v>13.7</v>
       </c>
       <c r="Y39" s="8" t="n">
-        <v>68.7</v>
+        <v>52.9</v>
       </c>
       <c r="Z39" s="8" t="n">
-        <v>8.1</v>
+        <v>12.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3846,19 +3846,19 @@
         <v>10.3</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>98</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q40" s="8" t="n">
         <v>22</v>
       </c>
       <c r="R40" s="8" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="S40" s="8" t="n">
         <v>18.4</v>
@@ -3876,13 +3876,13 @@
         <v>16.8</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>19.1</v>
+        <v>17.1</v>
       </c>
       <c r="Y40" s="8" t="n">
-        <v>83.3</v>
+        <v>74.7</v>
       </c>
       <c r="Z40" s="8" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3931,13 +3931,13 @@
         <v>8.6</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>98.7</v>
+        <v>97.5</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q41" s="8" t="n">
         <v>23.4</v>
@@ -3946,13 +3946,13 @@
         <v>17.4</v>
       </c>
       <c r="S41" s="8" t="n">
-        <v>19.9</v>
+        <v>15.8</v>
       </c>
       <c r="T41" s="8" t="n">
-        <v>69</v>
+        <v>54.8</v>
       </c>
       <c r="U41" s="8" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="V41" s="8" t="n">
         <v>22</v>
@@ -3961,13 +3961,13 @@
         <v>18.5</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>21.3</v>
+        <v>18.9</v>
       </c>
       <c r="Y41" s="8" t="n">
-        <v>80.5</v>
+        <v>71.5</v>
       </c>
       <c r="Z41" s="8" t="n">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4016,13 +4016,13 @@
         <v>11.3</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>96.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q42" s="8" t="n">
         <v>26.6</v>
@@ -4031,13 +4031,13 @@
         <v>17.6</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>20.1</v>
+        <v>14</v>
       </c>
       <c r="T42" s="8" t="n">
-        <v>57.7</v>
+        <v>40.1</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>14.7</v>
+        <v>20.9</v>
       </c>
       <c r="V42" s="8" t="n">
         <v>22</v>
@@ -4255,7 +4255,7 @@
       <c r="M46" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="8" t="n">
+      <c r="N46" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
@@ -4271,13 +4271,13 @@
         <v>17.7</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>20.2</v>
+        <v>15.5</v>
       </c>
       <c r="T46" s="8" t="n">
-        <v>65.09999999999999</v>
+        <v>49.7</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>10.9</v>
+        <v>15.6</v>
       </c>
       <c r="V46" s="8" t="n">
         <v>21.3</v>
@@ -4286,13 +4286,13 @@
         <v>16.8</v>
       </c>
       <c r="X46" s="8" t="n">
-        <v>19.1</v>
+        <v>16.1</v>
       </c>
       <c r="Y46" s="8" t="n">
-        <v>75.5</v>
+        <v>63.4</v>
       </c>
       <c r="Z46" s="8" t="n">
-        <v>6.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
